--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.41 ± 0.14</t>
+          <t>0.39 ± 0.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.24 ± 0.10</t>
+          <t>0.27 ± 0.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.62 ± 0.49</t>
+          <t>0.64 ± 0.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.35 ± 0.48</t>
+          <t>0.36 ± 0.48</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -503,17 +503,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -533,17 +533,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.00</t>
         </is>
       </c>
       <c r="F4" t="n">
